--- a/core/static/Plenty.xlsx
+++ b/core/static/Plenty.xlsx
@@ -19,6 +19,7 @@
     <definedName name="Plenty">Plenty!$A$1:$G$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
